--- a/Excel praticee tasks.xlsx
+++ b/Excel praticee tasks.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Music\Exel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8180" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="89">
   <si>
     <t>Name</t>
   </si>
@@ -233,6 +234,75 @@
   </si>
   <si>
     <t>Kavita</t>
+  </si>
+  <si>
+    <t>Task 3 Student MarkSheet</t>
+  </si>
+  <si>
+    <t>Roll No</t>
+  </si>
+  <si>
+    <t>Student Name</t>
+  </si>
+  <si>
+    <t>Maths</t>
+  </si>
+  <si>
+    <t>Science</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Percentage</t>
+  </si>
+  <si>
+    <t>Aakash</t>
+  </si>
+  <si>
+    <t>Bhavya</t>
+  </si>
+  <si>
+    <t>Chirag</t>
+  </si>
+  <si>
+    <t>Divya</t>
+  </si>
+  <si>
+    <t>Esha</t>
+  </si>
+  <si>
+    <t>Farhan</t>
+  </si>
+  <si>
+    <t>Gauri</t>
+  </si>
+  <si>
+    <t>Harsh</t>
+  </si>
+  <si>
+    <t>Isha</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Jay</t>
+  </si>
+  <si>
+    <t>Kavya</t>
+  </si>
+  <si>
+    <t>Laksh</t>
+  </si>
+  <si>
+    <t>Mehul</t>
+  </si>
+  <si>
+    <t>Nisha</t>
+  </si>
+  <si>
+    <t>Om</t>
   </si>
 </sst>
 </file>
@@ -242,7 +312,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,8 +352,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -305,6 +382,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -373,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -381,6 +464,10 @@
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -393,25 +480,18 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -424,11 +504,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -753,13 +833,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1141,302 +1221,302 @@
   <cols>
     <col min="1" max="1" width="38.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.453125" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="9">
         <v>44516</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="9">
         <v>72601</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="9">
         <v>29996</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="9">
         <v>83606</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="8" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="9">
         <v>7751</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="9">
         <v>72095</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="9">
         <v>70451</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="9">
         <v>51979</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="8" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="9">
         <v>87244</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="9">
         <v>82472</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="9">
         <v>81683</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="9">
         <v>89266</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="8" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="9">
         <v>47858</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="9">
         <v>31133</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="9">
         <v>10765</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="9">
         <v>38327</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="8" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="9">
         <v>63702</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="13">
+      <c r="C20" s="9">
         <v>92964</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="13">
+      <c r="C21" s="9">
         <v>9828</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1448,16 +1528,430 @@
     <cfRule type="cellIs" priority="3" operator="greaterThan">
       <formula>50358</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>50358</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>50358</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="26" x14ac:dyDescent="0.6">
+      <c r="A1" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="17">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="17">
+        <v>78</v>
+      </c>
+      <c r="D3" s="17">
+        <v>82</v>
+      </c>
+      <c r="E3" s="17">
+        <v>74</v>
+      </c>
+      <c r="F3" s="17">
+        <v>78</v>
+      </c>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="17">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="17">
+        <v>65</v>
+      </c>
+      <c r="D4" s="17">
+        <v>70</v>
+      </c>
+      <c r="E4" s="17">
+        <v>68</v>
+      </c>
+      <c r="F4" s="17">
+        <v>67.666666669999998</v>
+      </c>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="17">
+        <v>3</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="17">
+        <v>90</v>
+      </c>
+      <c r="D5" s="17">
+        <v>88</v>
+      </c>
+      <c r="E5" s="17">
+        <v>92</v>
+      </c>
+      <c r="F5" s="17">
+        <v>90</v>
+      </c>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="17">
+        <v>4</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="17">
+        <v>35</v>
+      </c>
+      <c r="D6" s="17">
+        <v>40</v>
+      </c>
+      <c r="E6" s="17">
+        <v>38</v>
+      </c>
+      <c r="F6" s="17">
+        <v>37.666666669999998</v>
+      </c>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="17">
+        <v>5</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="17">
+        <v>55</v>
+      </c>
+      <c r="D7" s="17">
+        <v>60</v>
+      </c>
+      <c r="E7" s="17">
+        <v>58</v>
+      </c>
+      <c r="F7" s="17">
+        <v>57.666666669999998</v>
+      </c>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="17">
+        <v>6</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="17">
+        <v>72</v>
+      </c>
+      <c r="D8" s="17">
+        <v>75</v>
+      </c>
+      <c r="E8" s="17">
+        <v>70</v>
+      </c>
+      <c r="F8" s="17">
+        <v>72.333333330000002</v>
+      </c>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="17">
+        <v>7</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="17">
+        <v>85</v>
+      </c>
+      <c r="D9" s="17">
+        <v>88</v>
+      </c>
+      <c r="E9" s="17">
+        <v>82</v>
+      </c>
+      <c r="F9" s="17">
+        <v>85</v>
+      </c>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="17">
+        <v>8</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="17">
+        <v>48</v>
+      </c>
+      <c r="D10" s="17">
+        <v>52</v>
+      </c>
+      <c r="E10" s="17">
+        <v>50</v>
+      </c>
+      <c r="F10" s="17">
+        <v>50</v>
+      </c>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="17">
+        <v>9</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="17">
+        <v>95</v>
+      </c>
+      <c r="D11" s="17">
+        <v>92</v>
+      </c>
+      <c r="E11" s="17">
+        <v>94</v>
+      </c>
+      <c r="F11" s="17">
+        <v>93.666666669999998</v>
+      </c>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="17">
+        <v>10</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="17">
+        <v>33</v>
+      </c>
+      <c r="D12" s="17">
+        <v>38</v>
+      </c>
+      <c r="E12" s="17">
+        <v>35</v>
+      </c>
+      <c r="F12" s="17">
+        <v>35.333333330000002</v>
+      </c>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="17">
+        <v>11</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="17">
+        <v>68</v>
+      </c>
+      <c r="D13" s="17">
+        <v>72</v>
+      </c>
+      <c r="E13" s="17">
+        <v>70</v>
+      </c>
+      <c r="F13" s="17">
+        <v>70</v>
+      </c>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="17">
+        <v>12</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="17">
+        <v>80</v>
+      </c>
+      <c r="D14" s="17">
+        <v>78</v>
+      </c>
+      <c r="E14" s="17">
+        <v>76</v>
+      </c>
+      <c r="F14" s="17">
+        <v>78</v>
+      </c>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="17">
+        <v>13</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="17">
+        <v>58</v>
+      </c>
+      <c r="D15" s="17">
+        <v>55</v>
+      </c>
+      <c r="E15" s="17">
+        <v>60</v>
+      </c>
+      <c r="F15" s="17">
+        <v>57.666666669999998</v>
+      </c>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="17">
+        <v>14</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="17">
+        <v>88</v>
+      </c>
+      <c r="D16" s="17">
+        <v>90</v>
+      </c>
+      <c r="E16" s="17">
+        <v>86</v>
+      </c>
+      <c r="F16" s="17">
+        <v>88</v>
+      </c>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="17">
+        <v>42</v>
+      </c>
+      <c r="D17" s="17">
+        <v>45</v>
+      </c>
+      <c r="E17" s="17">
+        <v>40</v>
+      </c>
+      <c r="F17" s="17">
+        <v>42.333333330000002</v>
+      </c>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>